--- a/Luca/random_benchmark_results.xlsx
+++ b/Luca/random_benchmark_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -933,6 +933,98 @@
       <c r="AD5" t="inlineStr">
         <is>
           <t>2026-05-14 16:48:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3a8584ef93f94e68ba8df32d8fa83a91</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>random baseline</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.2480496287245042</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2089502093867931</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2079138290743755</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2512167727442906</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.207724313913171</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2415623814941221</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2096848597277456</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2537313432835821</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.2104711430965842</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.2455677102980008</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:41:54</t>
         </is>
       </c>
     </row>
